--- a/data files/AI Searches and Job Postings-2.xlsx
+++ b/data files/AI Searches and Job Postings-2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kerry\Documents\school\UWB\BBECN 382, Intro To Econometrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AC7AF2-67AE-495C-B505-417D96CA36E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE30D665-BA34-4D5B-822C-FC5A88649078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="67">
   <si>
     <t>Date</t>
   </si>
@@ -220,13 +220,17 @@
   <si>
     <t>HiringLabNationalAI</t>
   </si>
+  <si>
+    <t>Unemployment Rate</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -239,6 +243,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -246,6 +251,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -269,11 +275,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,10 +503,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,8 +522,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -532,8 +542,11 @@
       <c r="E2" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="4">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -549,8 +562,11 @@
       <c r="E3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="4">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -566,8 +582,11 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="4">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -583,8 +602,11 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -600,8 +622,11 @@
       <c r="E6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="4">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -617,8 +642,11 @@
       <c r="E7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="4">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -634,8 +662,11 @@
       <c r="E8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -651,8 +682,11 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="4">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -668,8 +702,11 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -685,8 +722,11 @@
       <c r="E11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="4">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -702,8 +742,11 @@
       <c r="E12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="4">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -719,8 +762,11 @@
       <c r="E13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="4">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -736,8 +782,11 @@
       <c r="E14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="4">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -753,8 +802,11 @@
       <c r="E15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="4">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -770,8 +822,11 @@
       <c r="E16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -787,8 +842,11 @@
       <c r="E17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="4">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -804,8 +862,11 @@
       <c r="E18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -821,8 +882,11 @@
       <c r="E19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="4">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -838,8 +902,11 @@
       <c r="E20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="4">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -855,8 +922,11 @@
       <c r="E21" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -872,8 +942,11 @@
       <c r="E22" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -889,8 +962,11 @@
       <c r="E23" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="4">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -906,8 +982,11 @@
       <c r="E24" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -923,8 +1002,11 @@
       <c r="E25" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="4">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -940,8 +1022,11 @@
       <c r="E26" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="4">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -957,8 +1042,11 @@
       <c r="E27" s="1">
         <v>17</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="4">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -974,8 +1062,11 @@
       <c r="E28" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="4">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -991,8 +1082,11 @@
       <c r="E29" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="4">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -1008,8 +1102,11 @@
       <c r="E30" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="4">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -1025,8 +1122,11 @@
       <c r="E31" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="4">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -1042,8 +1142,11 @@
       <c r="E32" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="4">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -1059,8 +1162,11 @@
       <c r="E33" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="4">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>37</v>
       </c>
@@ -1076,8 +1182,11 @@
       <c r="E34" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="4">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -1093,8 +1202,11 @@
       <c r="E35" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35" s="4">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -1110,8 +1222,11 @@
       <c r="E36" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" s="4">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
@@ -1127,8 +1242,11 @@
       <c r="E37" s="1">
         <v>29</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37" s="4">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>41</v>
       </c>
@@ -1144,8 +1262,11 @@
       <c r="E38" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" s="4">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
@@ -1161,8 +1282,11 @@
       <c r="E39" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -1178,8 +1302,11 @@
       <c r="E40" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40" s="4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -1195,8 +1322,11 @@
       <c r="E41" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41" s="4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -1212,8 +1342,11 @@
       <c r="E42" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>46</v>
       </c>
@@ -1229,8 +1362,11 @@
       <c r="E43" s="1">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>47</v>
       </c>
@@ -1246,8 +1382,11 @@
       <c r="E44" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44" s="4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>48</v>
       </c>
@@ -1263,8 +1402,11 @@
       <c r="E45" s="1">
         <v>41</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>49</v>
       </c>
@@ -1280,8 +1422,11 @@
       <c r="E46" s="1">
         <v>46</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
@@ -1297,8 +1442,11 @@
       <c r="E47" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47" s="4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>51</v>
       </c>
@@ -1314,8 +1462,11 @@
       <c r="E48" s="1">
         <v>61</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48" s="4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
@@ -1331,8 +1482,11 @@
       <c r="E49" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49" s="4">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>53</v>
       </c>
@@ -1348,8 +1502,11 @@
       <c r="E50" s="1">
         <v>80</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" s="4">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>54</v>
       </c>
@@ -1365,8 +1522,11 @@
       <c r="E51" s="1">
         <v>71</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>55</v>
       </c>
@@ -1382,8 +1542,11 @@
       <c r="E52" s="1">
         <v>82</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52" s="4">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
@@ -1399,8 +1562,11 @@
       <c r="E53" s="1">
         <v>85</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53" s="4">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -1416,8 +1582,11 @@
       <c r="E54" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
@@ -1433,8 +1602,9 @@
       <c r="E55" s="1">
         <v>95</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>59</v>
       </c>
@@ -1450,8 +1620,11 @@
       <c r="E56" s="1">
         <v>85</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="4">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>60</v>
       </c>
@@ -1467,8 +1640,11 @@
       <c r="E57" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>61</v>
       </c>
@@ -1484,8 +1660,11 @@
       <c r="E58" s="1">
         <v>77</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="4">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>62</v>
       </c>
@@ -1501,8 +1680,11 @@
       <c r="E59" s="1">
         <v>77</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>63</v>
       </c>
@@ -1518,8 +1700,11 @@
       <c r="E60" s="1">
         <v>82</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60" s="4">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>64</v>
       </c>
@@ -1535,22 +1720,25 @@
       <c r="E61" s="1">
         <v>78</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61" s="4">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -1583,6 +1771,9 @@
   </sheetPr>
   <dimension ref="A1:C1946"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
